--- a/data/nzd0258/nzd0258.xlsx
+++ b/data/nzd0258/nzd0258.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O350"/>
+  <dimension ref="A1:O351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18266,6 +18266,57 @@
       <c r="O350" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>360.22</v>
+      </c>
+      <c r="C351" t="n">
+        <v>354.58</v>
+      </c>
+      <c r="D351" t="n">
+        <v>348.2</v>
+      </c>
+      <c r="E351" t="n">
+        <v>339.26</v>
+      </c>
+      <c r="F351" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="G351" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="H351" t="n">
+        <v>343.44</v>
+      </c>
+      <c r="I351" t="n">
+        <v>342.55</v>
+      </c>
+      <c r="J351" t="n">
+        <v>339.62</v>
+      </c>
+      <c r="K351" t="n">
+        <v>334.68</v>
+      </c>
+      <c r="L351" t="n">
+        <v>331.15</v>
+      </c>
+      <c r="M351" t="n">
+        <v>334.98</v>
+      </c>
+      <c r="N351" t="n">
+        <v>333.1</v>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18280,7 +18331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21943,6 +21994,16 @@
       </c>
       <c r="B366" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -22111,28 +22172,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.185568881684715</v>
+        <v>1.192433920784001</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2846243081199071</v>
+        <v>0.2876123790529027</v>
       </c>
       <c r="M2" t="n">
-        <v>11.29411186052772</v>
+        <v>11.29788180460482</v>
       </c>
       <c r="N2" t="n">
-        <v>192.9019029753144</v>
+        <v>192.8147755214366</v>
       </c>
       <c r="O2" t="n">
-        <v>13.88891295153492</v>
+        <v>13.8857760143766</v>
       </c>
       <c r="P2" t="n">
-        <v>316.6484481229131</v>
+        <v>316.5771860577628</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22189,28 +22250,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9301651854901622</v>
+        <v>0.9374406378291753</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2483856758330801</v>
+        <v>0.2516512672745227</v>
       </c>
       <c r="M3" t="n">
-        <v>9.817711703473817</v>
+        <v>9.832496303529284</v>
       </c>
       <c r="N3" t="n">
-        <v>142.9583082813805</v>
+        <v>143.072226569674</v>
       </c>
       <c r="O3" t="n">
-        <v>11.95651739769488</v>
+        <v>11.96128030645859</v>
       </c>
       <c r="P3" t="n">
-        <v>316.8709247757004</v>
+        <v>316.7954024442055</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22267,28 +22328,28 @@
         <v>0.0755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.785563814439915</v>
+        <v>0.7924451457318832</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1088830128240402</v>
+        <v>0.1109615727202324</v>
       </c>
       <c r="M4" t="n">
-        <v>13.5627418035867</v>
+        <v>13.56065283209491</v>
       </c>
       <c r="N4" t="n">
-        <v>275.7771451437543</v>
+        <v>275.4540905475082</v>
       </c>
       <c r="O4" t="n">
-        <v>16.60653922838092</v>
+        <v>16.59680964967389</v>
       </c>
       <c r="P4" t="n">
-        <v>314.9771224658156</v>
+        <v>314.9056912806821</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22345,28 +22406,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3658995542173164</v>
+        <v>0.3653593673597018</v>
       </c>
       <c r="J5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K5" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04165567882761767</v>
+        <v>0.0417570146642352</v>
       </c>
       <c r="M5" t="n">
-        <v>10.42412848717718</v>
+        <v>10.39692630614223</v>
       </c>
       <c r="N5" t="n">
-        <v>168.1867800346792</v>
+        <v>167.7063773272431</v>
       </c>
       <c r="O5" t="n">
-        <v>12.96868459153353</v>
+        <v>12.95014970288927</v>
       </c>
       <c r="P5" t="n">
-        <v>330.7706697275182</v>
+        <v>330.7762770999576</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22423,28 +22484,28 @@
         <v>0.0959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6218961801085127</v>
+        <v>0.620555182037971</v>
       </c>
       <c r="J6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1480484981742741</v>
+        <v>0.1481807339358322</v>
       </c>
       <c r="M6" t="n">
-        <v>8.782520626043739</v>
+        <v>8.763903353329113</v>
       </c>
       <c r="N6" t="n">
-        <v>121.8685248154861</v>
+        <v>121.5361894053923</v>
       </c>
       <c r="O6" t="n">
-        <v>11.03940781090572</v>
+        <v>11.02434530506879</v>
       </c>
       <c r="P6" t="n">
-        <v>328.8674249188069</v>
+        <v>328.8813127836794</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22501,28 +22562,28 @@
         <v>0.0877</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5881913110793751</v>
+        <v>0.5844958978825386</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1690139737970965</v>
+        <v>0.1678183058989166</v>
       </c>
       <c r="M7" t="n">
-        <v>7.546771924568156</v>
+        <v>7.544080593422391</v>
       </c>
       <c r="N7" t="n">
-        <v>92.66814921151284</v>
+        <v>92.53804815381605</v>
       </c>
       <c r="O7" t="n">
-        <v>9.626429722982079</v>
+        <v>9.619669856799455</v>
       </c>
       <c r="P7" t="n">
-        <v>332.7227728007546</v>
+        <v>332.7611193982083</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22579,28 +22640,28 @@
         <v>0.0696</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4645284121232334</v>
+        <v>0.4638389137391355</v>
       </c>
       <c r="J8" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K8" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08152833909046897</v>
+        <v>0.08171706292535508</v>
       </c>
       <c r="M8" t="n">
-        <v>9.16968786049978</v>
+        <v>9.147597154969977</v>
       </c>
       <c r="N8" t="n">
-        <v>132.4353434119218</v>
+        <v>132.0616448016762</v>
       </c>
       <c r="O8" t="n">
-        <v>11.50805558780118</v>
+        <v>11.49180772557895</v>
       </c>
       <c r="P8" t="n">
-        <v>332.665576706998</v>
+        <v>332.6727315001352</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22657,28 +22718,28 @@
         <v>0.0615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.513818978716842</v>
+        <v>0.5120000166983613</v>
       </c>
       <c r="J9" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K9" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1087651508736884</v>
+        <v>0.1085863009570557</v>
       </c>
       <c r="M9" t="n">
-        <v>8.407995168030135</v>
+        <v>8.393837738426862</v>
       </c>
       <c r="N9" t="n">
-        <v>117.8541414564141</v>
+        <v>117.55004227114</v>
       </c>
       <c r="O9" t="n">
-        <v>10.85606473158732</v>
+        <v>10.84204972646501</v>
       </c>
       <c r="P9" t="n">
-        <v>332.6062687987</v>
+        <v>332.6251438204068</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22735,28 +22796,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3284856763340238</v>
+        <v>0.3268369530259134</v>
       </c>
       <c r="J10" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K10" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04768628334287572</v>
+        <v>0.04746964540252052</v>
       </c>
       <c r="M10" t="n">
-        <v>8.570305319385195</v>
+        <v>8.554189118749207</v>
       </c>
       <c r="N10" t="n">
-        <v>117.9952018376846</v>
+        <v>117.6831347566787</v>
       </c>
       <c r="O10" t="n">
-        <v>10.86255963563306</v>
+        <v>10.84818578181065</v>
       </c>
       <c r="P10" t="n">
-        <v>334.1773636738665</v>
+        <v>334.1944384534791</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22813,28 +22874,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2802915535993001</v>
+        <v>0.2769639593270631</v>
       </c>
       <c r="J11" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K11" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02676563776399021</v>
+        <v>0.02627311931687071</v>
       </c>
       <c r="M11" t="n">
-        <v>9.935555248600512</v>
+        <v>9.924829745591598</v>
       </c>
       <c r="N11" t="n">
-        <v>156.4244975958121</v>
+        <v>156.0849841035882</v>
       </c>
       <c r="O11" t="n">
-        <v>12.5069779561576</v>
+        <v>12.49339762048692</v>
       </c>
       <c r="P11" t="n">
-        <v>333.6139211990804</v>
+        <v>333.6483829784215</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22891,28 +22952,28 @@
         <v>0.1039</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4077566534664029</v>
+        <v>0.4001277752497711</v>
       </c>
       <c r="J12" t="n">
+        <v>350</v>
+      </c>
+      <c r="K12" t="n">
         <v>349</v>
       </c>
-      <c r="K12" t="n">
-        <v>348</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.04602821969056425</v>
+        <v>0.04450204341298825</v>
       </c>
       <c r="M12" t="n">
-        <v>10.91869935158778</v>
+        <v>10.92191217947255</v>
       </c>
       <c r="N12" t="n">
-        <v>187.5235484287192</v>
+        <v>187.5600190399585</v>
       </c>
       <c r="O12" t="n">
-        <v>13.69392377767305</v>
+        <v>13.69525534774575</v>
       </c>
       <c r="P12" t="n">
-        <v>334.7735098145331</v>
+        <v>334.852809798614</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22969,28 +23030,28 @@
         <v>0.0806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4441761855732291</v>
+        <v>0.4364823150069051</v>
       </c>
       <c r="J13" t="n">
+        <v>350</v>
+      </c>
+      <c r="K13" t="n">
         <v>349</v>
       </c>
-      <c r="K13" t="n">
-        <v>348</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.03439186586978771</v>
+        <v>0.03336525571227911</v>
       </c>
       <c r="M13" t="n">
-        <v>13.20087344436821</v>
+        <v>13.19467273143657</v>
       </c>
       <c r="N13" t="n">
-        <v>301.4380466642975</v>
+        <v>301.1579328263942</v>
       </c>
       <c r="O13" t="n">
-        <v>17.36197127817857</v>
+        <v>17.35390252440051</v>
       </c>
       <c r="P13" t="n">
-        <v>337.7850601785598</v>
+        <v>337.865035739331</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23047,28 +23108,28 @@
         <v>0.0444</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7952639733984671</v>
+        <v>0.7838332414551678</v>
       </c>
       <c r="J14" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K14" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L14" t="n">
-        <v>0.100707988855958</v>
+        <v>0.09823377200266192</v>
       </c>
       <c r="M14" t="n">
-        <v>12.73037012576958</v>
+        <v>12.75582498569998</v>
       </c>
       <c r="N14" t="n">
-        <v>310.1978862697544</v>
+        <v>310.6029629475535</v>
       </c>
       <c r="O14" t="n">
-        <v>17.61243555757563</v>
+        <v>17.62393154059427</v>
       </c>
       <c r="P14" t="n">
-        <v>333.7816250236758</v>
+        <v>333.8997524341658</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23106,7 +23167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O350"/>
+  <dimension ref="A1:O351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49983,6 +50044,83 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-38.42611216450818,174.6412499296552</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-38.425408363617365,174.64117591731295</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-38.42470345820548,174.64111026354786</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-38.42399474802128,174.64107352847077</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-38.42330410212915,174.64089919656928</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-38.42260656539784,174.6407772819758</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-38.4219140164318,174.64061302194153</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-38.42121675328849,174.64047675227226</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-38.420518178165764,174.64035039674258</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-38.419817114595446,174.64024683501893</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-38.419118437890155,174.6401274134244</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-38.41843224781785,174.63992521101008</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-38.41773635867463,174.63978723084935</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0258/nzd0258.xlsx
+++ b/data/nzd0258/nzd0258.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O351"/>
+  <dimension ref="A1:O352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18317,6 +18317,57 @@
       <c r="O351" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>360.11</v>
+      </c>
+      <c r="C352" t="n">
+        <v>355.82</v>
+      </c>
+      <c r="D352" t="n">
+        <v>347</v>
+      </c>
+      <c r="E352" t="n">
+        <v>342.29</v>
+      </c>
+      <c r="F352" t="n">
+        <v>342.24</v>
+      </c>
+      <c r="G352" t="n">
+        <v>339.38</v>
+      </c>
+      <c r="H352" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="I352" t="n">
+        <v>340.88</v>
+      </c>
+      <c r="J352" t="n">
+        <v>336.95</v>
+      </c>
+      <c r="K352" t="n">
+        <v>330.66</v>
+      </c>
+      <c r="L352" t="n">
+        <v>331.4</v>
+      </c>
+      <c r="M352" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="N352" t="n">
+        <v>338.49</v>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18331,7 +18382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B367"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22004,6 +22055,26 @@
       </c>
       <c r="B367" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -22172,28 +22243,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.192433920784001</v>
+        <v>1.199127205552487</v>
       </c>
       <c r="J2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K2" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2876123790529027</v>
+        <v>0.2905857869197164</v>
       </c>
       <c r="M2" t="n">
-        <v>11.29788180460482</v>
+        <v>11.30061825453731</v>
       </c>
       <c r="N2" t="n">
-        <v>192.8147755214366</v>
+        <v>192.703136263916</v>
       </c>
       <c r="O2" t="n">
-        <v>13.8857760143766</v>
+        <v>13.88175551808618</v>
       </c>
       <c r="P2" t="n">
-        <v>316.5771860577628</v>
+        <v>316.5073263515482</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22250,28 +22321,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9374406378291753</v>
+        <v>0.9452815866860004</v>
       </c>
       <c r="J3" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K3" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2516512672745227</v>
+        <v>0.2550543796320653</v>
       </c>
       <c r="M3" t="n">
-        <v>9.832496303529284</v>
+        <v>9.850071302119332</v>
       </c>
       <c r="N3" t="n">
-        <v>143.072226569674</v>
+        <v>143.2672536560526</v>
       </c>
       <c r="O3" t="n">
-        <v>11.96128030645859</v>
+        <v>11.96942996370557</v>
       </c>
       <c r="P3" t="n">
-        <v>316.7954024442055</v>
+        <v>316.713564243303</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22328,28 +22399,28 @@
         <v>0.0755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7924451457318832</v>
+        <v>0.7985940636379871</v>
       </c>
       <c r="J4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K4" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1109615727202324</v>
+        <v>0.1129167496908249</v>
       </c>
       <c r="M4" t="n">
-        <v>13.56065283209491</v>
+        <v>13.5543127175059</v>
       </c>
       <c r="N4" t="n">
-        <v>275.4540905475082</v>
+        <v>275.0368713273877</v>
       </c>
       <c r="O4" t="n">
-        <v>16.59680964967389</v>
+        <v>16.58423562686528</v>
       </c>
       <c r="P4" t="n">
-        <v>314.9056912806821</v>
+        <v>314.8415132853755</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22406,28 +22477,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3653593673597018</v>
+        <v>0.3664276233834137</v>
       </c>
       <c r="J5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K5" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0417570146642352</v>
+        <v>0.04221293749276622</v>
       </c>
       <c r="M5" t="n">
-        <v>10.39692630614223</v>
+        <v>10.37306612722618</v>
       </c>
       <c r="N5" t="n">
-        <v>167.7063773272431</v>
+        <v>167.2370725698276</v>
       </c>
       <c r="O5" t="n">
-        <v>12.95014970288927</v>
+        <v>12.9320173433934</v>
       </c>
       <c r="P5" t="n">
-        <v>330.7762770999576</v>
+        <v>330.7651274096994</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22484,28 +22555,28 @@
         <v>0.0959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.620555182037971</v>
+        <v>0.6190455041377778</v>
       </c>
       <c r="J6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K6" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1481807339358322</v>
+        <v>0.1482452150812594</v>
       </c>
       <c r="M6" t="n">
-        <v>8.763903353329113</v>
+        <v>8.746143460544705</v>
       </c>
       <c r="N6" t="n">
-        <v>121.5361894053923</v>
+        <v>121.2104204038065</v>
       </c>
       <c r="O6" t="n">
-        <v>11.02434530506879</v>
+        <v>11.0095604091992</v>
       </c>
       <c r="P6" t="n">
-        <v>328.8813127836794</v>
+        <v>328.8970333150827</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22562,28 +22633,28 @@
         <v>0.0877</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5844958978825386</v>
+        <v>0.5798664041757229</v>
       </c>
       <c r="J7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1678183058989166</v>
+        <v>0.1660665872208376</v>
       </c>
       <c r="M7" t="n">
-        <v>7.544080593422391</v>
+        <v>7.545912667660814</v>
       </c>
       <c r="N7" t="n">
-        <v>92.53804815381605</v>
+        <v>92.48421770586573</v>
       </c>
       <c r="O7" t="n">
-        <v>9.619669856799455</v>
+        <v>9.616871513432304</v>
       </c>
       <c r="P7" t="n">
-        <v>332.7611193982083</v>
+        <v>332.8094196928621</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22640,28 +22711,28 @@
         <v>0.0696</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4638389137391355</v>
+        <v>0.4585151856664511</v>
       </c>
       <c r="J8" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K8" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08171706292535508</v>
+        <v>0.08025732795976181</v>
       </c>
       <c r="M8" t="n">
-        <v>9.147597154969977</v>
+        <v>9.152962102276152</v>
       </c>
       <c r="N8" t="n">
-        <v>132.0616448016762</v>
+        <v>131.9628556974376</v>
       </c>
       <c r="O8" t="n">
-        <v>11.49180772557895</v>
+        <v>11.48750868106038</v>
       </c>
       <c r="P8" t="n">
-        <v>332.6727315001352</v>
+        <v>332.7282748599176</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22718,28 +22789,28 @@
         <v>0.0615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5120000166983613</v>
+        <v>0.5092656286901358</v>
       </c>
       <c r="J9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1085863009570557</v>
+        <v>0.1080305310399705</v>
       </c>
       <c r="M9" t="n">
-        <v>8.393837738426862</v>
+        <v>8.384729519493821</v>
       </c>
       <c r="N9" t="n">
-        <v>117.55004227114</v>
+        <v>117.2883367872366</v>
       </c>
       <c r="O9" t="n">
-        <v>10.84204972646501</v>
+        <v>10.8299739975328</v>
       </c>
       <c r="P9" t="n">
-        <v>332.6251438204068</v>
+        <v>332.6536721552226</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22796,28 +22867,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3268369530259134</v>
+        <v>0.323742031639531</v>
       </c>
       <c r="J10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K10" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04746964540252052</v>
+        <v>0.04682875159321698</v>
       </c>
       <c r="M10" t="n">
-        <v>8.554189118749207</v>
+        <v>8.545534480423633</v>
       </c>
       <c r="N10" t="n">
-        <v>117.6831347566787</v>
+        <v>117.4403783247253</v>
       </c>
       <c r="O10" t="n">
-        <v>10.84818578181065</v>
+        <v>10.83699120257672</v>
       </c>
       <c r="P10" t="n">
-        <v>334.1944384534791</v>
+        <v>334.2266663935176</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22874,28 +22945,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2769639593270631</v>
+        <v>0.2714846498456419</v>
       </c>
       <c r="J11" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K11" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02627311931687071</v>
+        <v>0.02536035628055988</v>
       </c>
       <c r="M11" t="n">
-        <v>9.924829745591598</v>
+        <v>9.925871279666007</v>
       </c>
       <c r="N11" t="n">
-        <v>156.0849841035882</v>
+        <v>155.9337747543476</v>
       </c>
       <c r="O11" t="n">
-        <v>12.49339762048692</v>
+        <v>12.48734458379153</v>
       </c>
       <c r="P11" t="n">
-        <v>333.6483829784215</v>
+        <v>333.7054399551179</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22952,28 +23023,28 @@
         <v>0.1039</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4001277752497711</v>
+        <v>0.3926564574215652</v>
       </c>
       <c r="J12" t="n">
+        <v>351</v>
+      </c>
+      <c r="K12" t="n">
         <v>350</v>
       </c>
-      <c r="K12" t="n">
-        <v>349</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.04450204341298825</v>
+        <v>0.04303565017172006</v>
       </c>
       <c r="M12" t="n">
-        <v>10.92191217947255</v>
+        <v>10.92483216434893</v>
       </c>
       <c r="N12" t="n">
-        <v>187.5600190399585</v>
+        <v>187.5704351686824</v>
       </c>
       <c r="O12" t="n">
-        <v>13.69525534774575</v>
+        <v>13.6956356248508</v>
       </c>
       <c r="P12" t="n">
-        <v>334.852809798614</v>
+        <v>334.9308946502366</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23030,28 +23101,28 @@
         <v>0.0806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4364823150069051</v>
+        <v>0.4291156475188492</v>
       </c>
       <c r="J13" t="n">
+        <v>351</v>
+      </c>
+      <c r="K13" t="n">
         <v>350</v>
       </c>
-      <c r="K13" t="n">
-        <v>349</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.03336525571227911</v>
+        <v>0.03240375073224244</v>
       </c>
       <c r="M13" t="n">
-        <v>13.19467273143657</v>
+        <v>13.18683061492593</v>
       </c>
       <c r="N13" t="n">
-        <v>301.1579328263942</v>
+        <v>300.8285866270034</v>
       </c>
       <c r="O13" t="n">
-        <v>17.35390252440051</v>
+        <v>17.3444108180994</v>
       </c>
       <c r="P13" t="n">
-        <v>337.865035739331</v>
+        <v>337.942026860708</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23108,28 +23179,28 @@
         <v>0.0444</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7838332414551678</v>
+        <v>0.775321352078702</v>
       </c>
       <c r="J14" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K14" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09823377200266192</v>
+        <v>0.09660149043130606</v>
       </c>
       <c r="M14" t="n">
-        <v>12.75582498569998</v>
+        <v>12.76501898056599</v>
       </c>
       <c r="N14" t="n">
-        <v>310.6029629475535</v>
+        <v>310.4255139211734</v>
       </c>
       <c r="O14" t="n">
-        <v>17.62393154059427</v>
+        <v>17.61889650123337</v>
       </c>
       <c r="P14" t="n">
-        <v>333.8997524341658</v>
+        <v>333.9881998433571</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23167,7 +23238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O351"/>
+  <dimension ref="A1:O352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50121,6 +50192,83 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-38.42611200130463,174.64125117234983</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-38.425410203360244,174.64116190888944</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-38.42470167781186,174.6411238199554</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-38.42399924350577,174.6410392988721</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-38.42330371638117,174.6409021337353</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-38.422604013540685,174.64079671227523</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-38.42190091508836,174.64070998271455</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-38.42121402762016,174.64049556203665</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-38.42051364590992,174.64038042785896</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-38.41981029077258,174.64029204997686</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-38.4191188622547,174.6401246015751</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-38.41843321535986,174.63991880005167</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-38.417745507821564,174.63972660848557</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0258/nzd0258.xlsx
+++ b/data/nzd0258/nzd0258.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O352"/>
+  <dimension ref="A1:O353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18368,6 +18368,57 @@
       <c r="O352" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>357.25</v>
+      </c>
+      <c r="C353" t="n">
+        <v>354.95</v>
+      </c>
+      <c r="D353" t="n">
+        <v>352.95</v>
+      </c>
+      <c r="E353" t="n">
+        <v>345.01</v>
+      </c>
+      <c r="F353" t="n">
+        <v>344.22</v>
+      </c>
+      <c r="G353" t="n">
+        <v>338.53</v>
+      </c>
+      <c r="H353" t="n">
+        <v>334.76</v>
+      </c>
+      <c r="I353" t="n">
+        <v>340.54</v>
+      </c>
+      <c r="J353" t="n">
+        <v>341.29</v>
+      </c>
+      <c r="K353" t="n">
+        <v>338.03</v>
+      </c>
+      <c r="L353" t="n">
+        <v>336.54</v>
+      </c>
+      <c r="M353" t="n">
+        <v>336.03</v>
+      </c>
+      <c r="N353" t="n">
+        <v>340.51</v>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18382,7 +18433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22075,6 +22126,16 @@
       </c>
       <c r="B369" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -22243,28 +22304,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.199127205552487</v>
+        <v>1.204174225764966</v>
       </c>
       <c r="J2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2905857869197164</v>
+        <v>0.2932037419609934</v>
       </c>
       <c r="M2" t="n">
-        <v>11.30061825453731</v>
+        <v>11.29459639824314</v>
       </c>
       <c r="N2" t="n">
-        <v>192.703136263916</v>
+        <v>192.40352858277</v>
       </c>
       <c r="O2" t="n">
-        <v>13.88175551808618</v>
+        <v>13.87095990127468</v>
       </c>
       <c r="P2" t="n">
-        <v>316.5073263515482</v>
+        <v>316.4544784881001</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22321,28 +22382,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9452815866860004</v>
+        <v>0.9525381766370322</v>
       </c>
       <c r="J3" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2550543796320653</v>
+        <v>0.2583439322151653</v>
       </c>
       <c r="M3" t="n">
-        <v>9.850071302119332</v>
+        <v>9.863923154237682</v>
       </c>
       <c r="N3" t="n">
-        <v>143.2672536560526</v>
+        <v>143.376744458405</v>
       </c>
       <c r="O3" t="n">
-        <v>11.96942996370557</v>
+        <v>11.97400285862689</v>
       </c>
       <c r="P3" t="n">
-        <v>316.713564243303</v>
+        <v>316.6375797497433</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22399,28 +22460,28 @@
         <v>0.0755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7985940636379871</v>
+        <v>0.8078380832546885</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1129167496908249</v>
+        <v>0.1154987360211186</v>
       </c>
       <c r="M4" t="n">
-        <v>13.5543127175059</v>
+        <v>13.56401820223108</v>
       </c>
       <c r="N4" t="n">
-        <v>275.0368713273877</v>
+        <v>275.0929858458278</v>
       </c>
       <c r="O4" t="n">
-        <v>16.58423562686528</v>
+        <v>16.58592734355929</v>
       </c>
       <c r="P4" t="n">
-        <v>314.8415132853755</v>
+        <v>314.7447182130658</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22477,28 +22538,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3664276233834137</v>
+        <v>0.3689319040754525</v>
       </c>
       <c r="J5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04221293749276622</v>
+        <v>0.04298055332050765</v>
       </c>
       <c r="M5" t="n">
-        <v>10.37306612722618</v>
+        <v>10.35720742053589</v>
       </c>
       <c r="N5" t="n">
-        <v>167.2370725698276</v>
+        <v>166.8210429634716</v>
       </c>
       <c r="O5" t="n">
-        <v>12.9320173433934</v>
+        <v>12.91592207174817</v>
       </c>
       <c r="P5" t="n">
-        <v>330.7651274096994</v>
+        <v>330.738904831133</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22555,28 +22616,28 @@
         <v>0.0959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6190455041377778</v>
+        <v>0.6185867037789936</v>
       </c>
       <c r="J6" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1482452150812594</v>
+        <v>0.1487605537259231</v>
       </c>
       <c r="M6" t="n">
-        <v>8.746143460544705</v>
+        <v>8.723367933230811</v>
       </c>
       <c r="N6" t="n">
-        <v>121.2104204038065</v>
+        <v>120.866183150139</v>
       </c>
       <c r="O6" t="n">
-        <v>11.0095604091992</v>
+        <v>10.99391573326533</v>
       </c>
       <c r="P6" t="n">
-        <v>328.8970333150827</v>
+        <v>328.9018263847818</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22633,28 +22694,28 @@
         <v>0.0877</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5798664041757229</v>
+        <v>0.574809128904736</v>
       </c>
       <c r="J7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1660665872208376</v>
+        <v>0.1640480510306983</v>
       </c>
       <c r="M7" t="n">
-        <v>7.545912667660814</v>
+        <v>7.549722644288217</v>
       </c>
       <c r="N7" t="n">
-        <v>92.48421770586573</v>
+        <v>92.47218969646259</v>
       </c>
       <c r="O7" t="n">
-        <v>9.616871513432304</v>
+        <v>9.616246133313279</v>
       </c>
       <c r="P7" t="n">
-        <v>332.8094196928621</v>
+        <v>332.8623526703356</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22711,28 +22772,28 @@
         <v>0.0696</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4585151856664511</v>
+        <v>0.4531815936935271</v>
       </c>
       <c r="J8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08025732795976181</v>
+        <v>0.07879837878294982</v>
       </c>
       <c r="M8" t="n">
-        <v>9.152962102276152</v>
+        <v>9.158310917635392</v>
       </c>
       <c r="N8" t="n">
-        <v>131.9628556974376</v>
+        <v>131.8668173567946</v>
       </c>
       <c r="O8" t="n">
-        <v>11.48750868106038</v>
+        <v>11.48332779976234</v>
       </c>
       <c r="P8" t="n">
-        <v>332.7282748599176</v>
+        <v>332.7840999611089</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22789,28 +22850,28 @@
         <v>0.0615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5092656286901358</v>
+        <v>0.5063583173240408</v>
       </c>
       <c r="J9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1080305310399705</v>
+        <v>0.1073989495581612</v>
       </c>
       <c r="M9" t="n">
-        <v>8.384729519493821</v>
+        <v>8.376578003836656</v>
       </c>
       <c r="N9" t="n">
-        <v>117.2883367872366</v>
+        <v>117.0379872386297</v>
       </c>
       <c r="O9" t="n">
-        <v>10.8299739975328</v>
+        <v>10.8184096446118</v>
       </c>
       <c r="P9" t="n">
-        <v>332.6536721552226</v>
+        <v>332.6841021078756</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22867,28 +22928,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.323742031639531</v>
+        <v>0.3229928414992438</v>
       </c>
       <c r="J10" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K10" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04682875159321698</v>
+        <v>0.0468686933105017</v>
       </c>
       <c r="M10" t="n">
-        <v>8.545534480423633</v>
+        <v>8.524957595669463</v>
       </c>
       <c r="N10" t="n">
-        <v>117.4403783247253</v>
+        <v>117.1103759319481</v>
       </c>
       <c r="O10" t="n">
-        <v>10.83699120257672</v>
+        <v>10.82175475290159</v>
       </c>
       <c r="P10" t="n">
-        <v>334.2266663935176</v>
+        <v>334.2344931540935</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22945,28 +23006,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2714846498456419</v>
+        <v>0.27000293415315</v>
       </c>
       <c r="J11" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K11" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02536035628055988</v>
+        <v>0.02522453308658723</v>
       </c>
       <c r="M11" t="n">
-        <v>9.925871279666007</v>
+        <v>9.905528978165036</v>
       </c>
       <c r="N11" t="n">
-        <v>155.9337747543476</v>
+        <v>155.5099255538192</v>
       </c>
       <c r="O11" t="n">
-        <v>12.48734458379153</v>
+        <v>12.47036188543938</v>
       </c>
       <c r="P11" t="n">
-        <v>333.7054399551179</v>
+        <v>333.720919381959</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23023,28 +23084,28 @@
         <v>0.1039</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3926564574215652</v>
+        <v>0.3880106228139231</v>
       </c>
       <c r="J12" t="n">
+        <v>352</v>
+      </c>
+      <c r="K12" t="n">
         <v>351</v>
       </c>
-      <c r="K12" t="n">
-        <v>350</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.04303565017172006</v>
+        <v>0.04224566427209842</v>
       </c>
       <c r="M12" t="n">
-        <v>10.92483216434893</v>
+        <v>10.91487406946044</v>
       </c>
       <c r="N12" t="n">
-        <v>187.5704351686824</v>
+        <v>187.2475569625458</v>
       </c>
       <c r="O12" t="n">
-        <v>13.6956356248508</v>
+        <v>13.68384291646706</v>
       </c>
       <c r="P12" t="n">
-        <v>334.9308946502366</v>
+        <v>334.9796059249232</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23101,28 +23162,28 @@
         <v>0.0806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4291156475188492</v>
+        <v>0.4220677176896032</v>
       </c>
       <c r="J13" t="n">
+        <v>352</v>
+      </c>
+      <c r="K13" t="n">
         <v>351</v>
       </c>
-      <c r="K13" t="n">
-        <v>350</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.03240375073224244</v>
+        <v>0.03150183234913884</v>
       </c>
       <c r="M13" t="n">
-        <v>13.18683061492593</v>
+        <v>13.17755446878848</v>
       </c>
       <c r="N13" t="n">
-        <v>300.8285866270034</v>
+        <v>300.4582993598007</v>
       </c>
       <c r="O13" t="n">
-        <v>17.3444108180994</v>
+        <v>17.33373298974577</v>
       </c>
       <c r="P13" t="n">
-        <v>337.942026860708</v>
+        <v>338.0159239480731</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23179,28 +23240,28 @@
         <v>0.0444</v>
       </c>
       <c r="I14" t="n">
-        <v>0.775321352078702</v>
+        <v>0.7679575638636845</v>
       </c>
       <c r="J14" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K14" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09660149043130606</v>
+        <v>0.0952805812245513</v>
       </c>
       <c r="M14" t="n">
-        <v>12.76501898056599</v>
+        <v>12.76796019943263</v>
       </c>
       <c r="N14" t="n">
-        <v>310.4255139211734</v>
+        <v>310.0719617531645</v>
       </c>
       <c r="O14" t="n">
-        <v>17.61889650123337</v>
+        <v>17.60886031954267</v>
       </c>
       <c r="P14" t="n">
-        <v>333.9881998433571</v>
+        <v>334.064966324515</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23238,7 +23299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O352"/>
+  <dimension ref="A1:O353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50269,6 +50330,83 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-38.42610775800752,174.6412834824079</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-38.425408912573076,174.6411717373802</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-38.424710505581615,174.64105660276087</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-38.42400327904775,174.64100857130765</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-38.42330665399852,174.64087976608548</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-38.422602752447304,174.64080631445756</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-38.42190077782126,174.64071099860138</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-38.42121347269331,174.64049939156934</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-38.42052101294363,174.6403316132333</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-38.4198228011013,174.64020915588037</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-38.419127587174714,174.64006678994565</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-38.41843403013183,174.6399134013497</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-38.417748936621884,174.63970388915394</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0258/nzd0258.xlsx
+++ b/data/nzd0258/nzd0258.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O353"/>
+  <dimension ref="A1:O354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18417,6 +18417,57 @@
         <v>340.51</v>
       </c>
       <c r="O353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>350.98</v>
+      </c>
+      <c r="C354" t="n">
+        <v>350.7</v>
+      </c>
+      <c r="D354" t="n">
+        <v>348.22</v>
+      </c>
+      <c r="E354" t="n">
+        <v>340.86</v>
+      </c>
+      <c r="F354" t="n">
+        <v>337.77</v>
+      </c>
+      <c r="G354" t="n">
+        <v>338.56</v>
+      </c>
+      <c r="H354" t="n">
+        <v>333.86</v>
+      </c>
+      <c r="I354" t="n">
+        <v>340.98</v>
+      </c>
+      <c r="J354" t="n">
+        <v>342.99</v>
+      </c>
+      <c r="K354" t="n">
+        <v>342.64</v>
+      </c>
+      <c r="L354" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="M354" t="n">
+        <v>344.41</v>
+      </c>
+      <c r="N354" t="n">
+        <v>352.03</v>
+      </c>
+      <c r="O354" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18433,7 +18484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B370"/>
+  <dimension ref="A1:B371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22136,6 +22187,16 @@
       </c>
       <c r="B370" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -22304,28 +22365,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.204174225764966</v>
+        <v>1.205780311295179</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2932037419609934</v>
+        <v>0.2948826646386216</v>
       </c>
       <c r="M2" t="n">
-        <v>11.29459639824314</v>
+        <v>11.27071575996569</v>
       </c>
       <c r="N2" t="n">
-        <v>192.40352858277</v>
+        <v>191.8809264064932</v>
       </c>
       <c r="O2" t="n">
-        <v>13.87095990127468</v>
+        <v>13.85210909596417</v>
       </c>
       <c r="P2" t="n">
-        <v>316.4544784881001</v>
+        <v>316.4376248698889</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22382,28 +22443,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9525381766370322</v>
+        <v>0.9574117636444152</v>
       </c>
       <c r="J3" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K3" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2583439322151653</v>
+        <v>0.2610581185547751</v>
       </c>
       <c r="M3" t="n">
-        <v>9.863923154237682</v>
+        <v>9.864526624147638</v>
       </c>
       <c r="N3" t="n">
-        <v>143.376744458405</v>
+        <v>143.2035807629486</v>
       </c>
       <c r="O3" t="n">
-        <v>11.97400285862689</v>
+        <v>11.96676985501721</v>
       </c>
       <c r="P3" t="n">
-        <v>316.6375797497433</v>
+        <v>316.5864382798798</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22460,28 +22521,28 @@
         <v>0.0755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8078380832546885</v>
+        <v>0.8144205932240638</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1154987360211186</v>
+        <v>0.1175807407816002</v>
       </c>
       <c r="M4" t="n">
-        <v>13.56401820223108</v>
+        <v>13.55961687003416</v>
       </c>
       <c r="N4" t="n">
-        <v>275.0929858458278</v>
+        <v>274.7385235224331</v>
       </c>
       <c r="O4" t="n">
-        <v>16.58592734355929</v>
+        <v>16.57523826442423</v>
       </c>
       <c r="P4" t="n">
-        <v>314.7447182130658</v>
+        <v>314.6756439901753</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22538,28 +22599,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3689319040754525</v>
+        <v>0.3691791782675842</v>
       </c>
       <c r="J5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04298055332050765</v>
+        <v>0.04326493238241425</v>
       </c>
       <c r="M5" t="n">
-        <v>10.35720742053589</v>
+        <v>10.32905082529051</v>
       </c>
       <c r="N5" t="n">
-        <v>166.8210429634716</v>
+        <v>166.3463751148628</v>
       </c>
       <c r="O5" t="n">
-        <v>12.91592207174817</v>
+        <v>12.89753368341648</v>
       </c>
       <c r="P5" t="n">
-        <v>330.738904831133</v>
+        <v>330.7363100348103</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22616,28 +22677,28 @@
         <v>0.0959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6185867037789936</v>
+        <v>0.6146797096287132</v>
       </c>
       <c r="J6" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1487605537259231</v>
+        <v>0.1477038936257223</v>
       </c>
       <c r="M6" t="n">
-        <v>8.723367933230811</v>
+        <v>8.717229310630335</v>
       </c>
       <c r="N6" t="n">
-        <v>120.866183150139</v>
+        <v>120.673380252863</v>
       </c>
       <c r="O6" t="n">
-        <v>10.99391573326533</v>
+        <v>10.98514361548646</v>
       </c>
       <c r="P6" t="n">
-        <v>328.9018263847818</v>
+        <v>328.942730432045</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22694,28 +22755,28 @@
         <v>0.0877</v>
       </c>
       <c r="I7" t="n">
-        <v>0.574809128904736</v>
+        <v>0.5698199595495249</v>
       </c>
       <c r="J7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1640480510306983</v>
+        <v>0.1620663854801311</v>
       </c>
       <c r="M7" t="n">
-        <v>7.549722644288217</v>
+        <v>7.553066701253698</v>
       </c>
       <c r="N7" t="n">
-        <v>92.47218969646259</v>
+        <v>92.45559533024007</v>
       </c>
       <c r="O7" t="n">
-        <v>9.616246133313279</v>
+        <v>9.615383264864697</v>
       </c>
       <c r="P7" t="n">
-        <v>332.8623526703356</v>
+        <v>332.9146840876786</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22772,28 +22833,28 @@
         <v>0.0696</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4531815936935271</v>
+        <v>0.4474261415589558</v>
       </c>
       <c r="J8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07879837878294982</v>
+        <v>0.07718255172385913</v>
       </c>
       <c r="M8" t="n">
-        <v>9.158310917635392</v>
+        <v>9.166437549907334</v>
       </c>
       <c r="N8" t="n">
-        <v>131.8668173567946</v>
+        <v>131.8197829076263</v>
       </c>
       <c r="O8" t="n">
-        <v>11.48332779976234</v>
+        <v>11.48127967204119</v>
       </c>
       <c r="P8" t="n">
-        <v>332.7840999611089</v>
+        <v>332.8444689215928</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22850,28 +22911,28 @@
         <v>0.0615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5063583173240408</v>
+        <v>0.5037118545905733</v>
       </c>
       <c r="J9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1073989495581612</v>
+        <v>0.1068728117957082</v>
       </c>
       <c r="M9" t="n">
-        <v>8.376578003836656</v>
+        <v>8.367095073030701</v>
       </c>
       <c r="N9" t="n">
-        <v>117.0379872386297</v>
+        <v>116.7754732101243</v>
       </c>
       <c r="O9" t="n">
-        <v>10.8184096446118</v>
+        <v>10.8062700877835</v>
       </c>
       <c r="P9" t="n">
-        <v>332.6841021078756</v>
+        <v>332.7118608660832</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22928,28 +22989,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3229928414992438</v>
+        <v>0.3231529347938255</v>
       </c>
       <c r="J10" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0468686933105017</v>
+        <v>0.0471621011217922</v>
       </c>
       <c r="M10" t="n">
-        <v>8.524957595669463</v>
+        <v>8.501551020400795</v>
       </c>
       <c r="N10" t="n">
-        <v>117.1103759319481</v>
+        <v>116.7769825875634</v>
       </c>
       <c r="O10" t="n">
-        <v>10.82175475290159</v>
+        <v>10.80633992559754</v>
       </c>
       <c r="P10" t="n">
-        <v>334.2344931540935</v>
+        <v>334.2328170666881</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23006,28 +23067,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.27000293415315</v>
+        <v>0.2709926900059801</v>
       </c>
       <c r="J11" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K11" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02522453308658723</v>
+        <v>0.02554155647368705</v>
       </c>
       <c r="M11" t="n">
-        <v>9.905528978165036</v>
+        <v>9.882472101028709</v>
       </c>
       <c r="N11" t="n">
-        <v>155.5099255538192</v>
+        <v>155.0766028528087</v>
       </c>
       <c r="O11" t="n">
-        <v>12.47036188543938</v>
+        <v>12.45297566257996</v>
       </c>
       <c r="P11" t="n">
-        <v>333.720919381959</v>
+        <v>333.7105571908152</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23084,28 +23145,28 @@
         <v>0.1039</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3880106228139231</v>
+        <v>0.3875131874242502</v>
       </c>
       <c r="J12" t="n">
+        <v>353</v>
+      </c>
+      <c r="K12" t="n">
         <v>352</v>
       </c>
-      <c r="K12" t="n">
-        <v>351</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.04224566427209842</v>
+        <v>0.04236673542703706</v>
       </c>
       <c r="M12" t="n">
-        <v>10.91487406946044</v>
+        <v>10.88611696194593</v>
       </c>
       <c r="N12" t="n">
-        <v>187.2475569625458</v>
+        <v>186.7180419731287</v>
       </c>
       <c r="O12" t="n">
-        <v>13.68384291646706</v>
+        <v>13.66448103563135</v>
       </c>
       <c r="P12" t="n">
-        <v>334.9796059249232</v>
+        <v>334.9848326388644</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23162,28 +23223,28 @@
         <v>0.0806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4220677176896032</v>
+        <v>0.4195807010180507</v>
       </c>
       <c r="J13" t="n">
+        <v>353</v>
+      </c>
+      <c r="K13" t="n">
         <v>352</v>
       </c>
-      <c r="K13" t="n">
-        <v>351</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.03150183234913884</v>
+        <v>0.03130545026922393</v>
       </c>
       <c r="M13" t="n">
-        <v>13.17755446878848</v>
+        <v>13.15002913277548</v>
       </c>
       <c r="N13" t="n">
-        <v>300.4582993598007</v>
+        <v>299.6656742248254</v>
       </c>
       <c r="O13" t="n">
-        <v>17.33373298974577</v>
+        <v>17.31085423151686</v>
       </c>
       <c r="P13" t="n">
-        <v>338.0159239480731</v>
+        <v>338.042055833699</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23240,28 +23301,28 @@
         <v>0.0444</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7679575638636845</v>
+        <v>0.7668174529667703</v>
       </c>
       <c r="J14" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K14" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0952805812245513</v>
+        <v>0.09550128478450004</v>
       </c>
       <c r="M14" t="n">
-        <v>12.76796019943263</v>
+        <v>12.73755813834693</v>
       </c>
       <c r="N14" t="n">
-        <v>310.0719617531645</v>
+        <v>309.1989605473606</v>
       </c>
       <c r="O14" t="n">
-        <v>17.60886031954267</v>
+        <v>17.58405415560816</v>
       </c>
       <c r="P14" t="n">
-        <v>334.064966324515</v>
+        <v>334.0768774754183</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23299,7 +23360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O353"/>
+  <dimension ref="A1:O354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50407,6 +50468,83 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-38.4260984553637,174.6413543159825</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-38.425402606991845,174.64121975011705</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-38.42470348787868,174.64111003760775</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-38.42399712187571,174.64105545343574</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-38.423297084471905,174.6409526303921</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-38.4226027969565,174.64080597555702</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-38.42189940514961,174.64072115746944</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-38.42121419083392,174.6404944357035</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-38.42052389864259,174.64031249229407</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-38.41983062639273,174.64015730487634</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-38.4191405896296,174.63998063484377</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-38.41844825465267,174.6398191489902</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-38.41776849088489,174.63957432143636</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0258/nzd0258.xlsx
+++ b/data/nzd0258/nzd0258.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O354"/>
+  <dimension ref="A1:O357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18470,6 +18470,159 @@
       <c r="O354" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:14+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>351.1</v>
+      </c>
+      <c r="C355" t="n">
+        <v>351.28</v>
+      </c>
+      <c r="D355" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="E355" t="n">
+        <v>340.86</v>
+      </c>
+      <c r="F355" t="n">
+        <v>338.03</v>
+      </c>
+      <c r="G355" t="n">
+        <v>338.83</v>
+      </c>
+      <c r="H355" t="n">
+        <v>334.76</v>
+      </c>
+      <c r="I355" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="J355" t="n">
+        <v>347.05</v>
+      </c>
+      <c r="K355" t="n">
+        <v>347.62</v>
+      </c>
+      <c r="L355" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="M355" t="n">
+        <v>349.23</v>
+      </c>
+      <c r="N355" t="n">
+        <v>355.47</v>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>351.2</v>
+      </c>
+      <c r="C356" t="n">
+        <v>350.83</v>
+      </c>
+      <c r="D356" t="n">
+        <v>348.25</v>
+      </c>
+      <c r="E356" t="n">
+        <v>342.39</v>
+      </c>
+      <c r="F356" t="n">
+        <v>339.96</v>
+      </c>
+      <c r="G356" t="n">
+        <v>339.42</v>
+      </c>
+      <c r="H356" t="n">
+        <v>336.92</v>
+      </c>
+      <c r="I356" t="n">
+        <v>345.11</v>
+      </c>
+      <c r="J356" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="K356" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="L356" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="M356" t="n">
+        <v>349.23</v>
+      </c>
+      <c r="N356" t="n">
+        <v>355.47</v>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>351.13</v>
+      </c>
+      <c r="C357" t="n">
+        <v>351.04</v>
+      </c>
+      <c r="D357" t="n">
+        <v>348.95</v>
+      </c>
+      <c r="E357" t="n">
+        <v>344.82</v>
+      </c>
+      <c r="F357" t="n">
+        <v>343.79</v>
+      </c>
+      <c r="G357" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="H357" t="n">
+        <v>338.75</v>
+      </c>
+      <c r="I357" t="n">
+        <v>349.49</v>
+      </c>
+      <c r="J357" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="K357" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="L357" t="n">
+        <v>355.14</v>
+      </c>
+      <c r="M357" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="N357" t="n">
+        <v>362.26</v>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18484,7 +18637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B371"/>
+  <dimension ref="A1:B374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22197,6 +22350,36 @@
       </c>
       <c r="B371" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>-0.79</v>
       </c>
     </row>
   </sheetData>
@@ -22365,28 +22548,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.205780311295179</v>
+        <v>1.210508628995744</v>
       </c>
       <c r="J2" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2948826646386216</v>
+        <v>0.2999291702824276</v>
       </c>
       <c r="M2" t="n">
-        <v>11.27071575996569</v>
+        <v>11.19910280944872</v>
       </c>
       <c r="N2" t="n">
-        <v>191.8809264064932</v>
+        <v>190.328657937932</v>
       </c>
       <c r="O2" t="n">
-        <v>13.85210909596417</v>
+        <v>13.79596527749806</v>
       </c>
       <c r="P2" t="n">
-        <v>316.4376248698889</v>
+        <v>316.3876915460861</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22443,28 +22626,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9574117636444152</v>
+        <v>0.9720896511852878</v>
       </c>
       <c r="J3" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2610581185547751</v>
+        <v>0.2692688768643808</v>
       </c>
       <c r="M3" t="n">
-        <v>9.864526624147638</v>
+        <v>9.868038586171355</v>
       </c>
       <c r="N3" t="n">
-        <v>143.2035807629486</v>
+        <v>142.7017226188771</v>
       </c>
       <c r="O3" t="n">
-        <v>11.96676985501721</v>
+        <v>11.94578262898154</v>
       </c>
       <c r="P3" t="n">
-        <v>316.5864382798798</v>
+        <v>316.4314337756569</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22521,28 +22704,28 @@
         <v>0.0755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8144205932240638</v>
+        <v>0.8341433720630894</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1175807407816002</v>
+        <v>0.1239353940311274</v>
       </c>
       <c r="M4" t="n">
-        <v>13.55961687003416</v>
+        <v>13.5479900958601</v>
       </c>
       <c r="N4" t="n">
-        <v>274.7385235224331</v>
+        <v>273.6952873910835</v>
       </c>
       <c r="O4" t="n">
-        <v>16.57523826442423</v>
+        <v>16.54373861589585</v>
       </c>
       <c r="P4" t="n">
-        <v>314.6756439901753</v>
+        <v>314.4673586018528</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22599,28 +22782,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3691791782675842</v>
+        <v>0.3727297508784115</v>
       </c>
       <c r="J5" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04326493238241425</v>
+        <v>0.0447570650164314</v>
       </c>
       <c r="M5" t="n">
-        <v>10.32905082529051</v>
+        <v>10.26056555980174</v>
       </c>
       <c r="N5" t="n">
-        <v>166.3463751148628</v>
+        <v>165.0005846187103</v>
       </c>
       <c r="O5" t="n">
-        <v>12.89753368341648</v>
+        <v>12.84525533489741</v>
       </c>
       <c r="P5" t="n">
-        <v>330.7363100348103</v>
+        <v>330.6987906126772</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22677,28 +22860,28 @@
         <v>0.0959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6146797096287132</v>
+        <v>0.6075467829353705</v>
       </c>
       <c r="J6" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1477038936257223</v>
+        <v>0.1466457239073778</v>
       </c>
       <c r="M6" t="n">
-        <v>8.717229310630335</v>
+        <v>8.677520785678368</v>
       </c>
       <c r="N6" t="n">
-        <v>120.673380252863</v>
+        <v>119.8675322208665</v>
       </c>
       <c r="O6" t="n">
-        <v>10.98514361548646</v>
+        <v>10.94840318132587</v>
       </c>
       <c r="P6" t="n">
-        <v>328.942730432045</v>
+        <v>329.0178511126178</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22755,28 +22938,28 @@
         <v>0.0877</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5698199595495249</v>
+        <v>0.5570899146924632</v>
       </c>
       <c r="J7" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1620663854801311</v>
+        <v>0.1574593907719544</v>
       </c>
       <c r="M7" t="n">
-        <v>7.553066701253698</v>
+        <v>7.55120951978305</v>
       </c>
       <c r="N7" t="n">
-        <v>92.45559533024007</v>
+        <v>92.21835858521445</v>
       </c>
       <c r="O7" t="n">
-        <v>9.615383264864697</v>
+        <v>9.603039028620806</v>
       </c>
       <c r="P7" t="n">
-        <v>332.9146840876786</v>
+        <v>333.0490398517105</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22833,28 +23016,28 @@
         <v>0.0696</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4474261415589558</v>
+        <v>0.4350873277042783</v>
       </c>
       <c r="J8" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K8" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07718255172385913</v>
+        <v>0.07416388313148425</v>
       </c>
       <c r="M8" t="n">
-        <v>9.166437549907334</v>
+        <v>9.160845802649721</v>
       </c>
       <c r="N8" t="n">
-        <v>131.8197829076263</v>
+        <v>131.2317879899634</v>
       </c>
       <c r="O8" t="n">
-        <v>11.48127967204119</v>
+        <v>11.45564437253372</v>
       </c>
       <c r="P8" t="n">
-        <v>332.8444689215928</v>
+        <v>332.9746860763987</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22911,28 +23094,28 @@
         <v>0.0615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5037118545905733</v>
+        <v>0.5036192327817853</v>
       </c>
       <c r="J9" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K9" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1068728117957082</v>
+        <v>0.1083977965757759</v>
       </c>
       <c r="M9" t="n">
-        <v>8.367095073030701</v>
+        <v>8.316871236202093</v>
       </c>
       <c r="N9" t="n">
-        <v>116.7754732101243</v>
+        <v>115.8510068764185</v>
       </c>
       <c r="O9" t="n">
-        <v>10.8062700877835</v>
+        <v>10.76341055968871</v>
       </c>
       <c r="P9" t="n">
-        <v>332.7118608660832</v>
+        <v>332.7128009345144</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22989,28 +23172,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3231529347938255</v>
+        <v>0.3263632622673985</v>
       </c>
       <c r="J10" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K10" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0471621011217922</v>
+        <v>0.04880689017892137</v>
       </c>
       <c r="M10" t="n">
-        <v>8.501551020400795</v>
+        <v>8.446923103804728</v>
       </c>
       <c r="N10" t="n">
-        <v>116.7769825875634</v>
+        <v>115.8436514509448</v>
       </c>
       <c r="O10" t="n">
-        <v>10.80633992559754</v>
+        <v>10.76306886770427</v>
       </c>
       <c r="P10" t="n">
-        <v>334.2328170666881</v>
+        <v>334.1990124367583</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23067,28 +23250,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2709926900059801</v>
+        <v>0.2772036120351268</v>
       </c>
       <c r="J11" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K11" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02554155647368705</v>
+        <v>0.02710425697953522</v>
       </c>
       <c r="M11" t="n">
-        <v>9.882472101028709</v>
+        <v>9.830892653529322</v>
       </c>
       <c r="N11" t="n">
-        <v>155.0766028528087</v>
+        <v>153.9248413751199</v>
       </c>
       <c r="O11" t="n">
-        <v>12.45297566257996</v>
+        <v>12.40664504913072</v>
       </c>
       <c r="P11" t="n">
-        <v>333.7105571908152</v>
+        <v>333.6451424511677</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23145,28 +23328,28 @@
         <v>0.1039</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3875131874242502</v>
+        <v>0.3969485999408561</v>
       </c>
       <c r="J12" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K12" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04236673542703706</v>
+        <v>0.04499428765591851</v>
       </c>
       <c r="M12" t="n">
-        <v>10.88611696194593</v>
+        <v>10.85040957651432</v>
       </c>
       <c r="N12" t="n">
-        <v>186.7180419731287</v>
+        <v>185.4997990837507</v>
       </c>
       <c r="O12" t="n">
-        <v>13.66448103563135</v>
+        <v>13.61983109600668</v>
       </c>
       <c r="P12" t="n">
-        <v>334.9848326388644</v>
+        <v>334.8850277458501</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23223,28 +23406,28 @@
         <v>0.0806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4195807010180507</v>
+        <v>0.4229352730176432</v>
       </c>
       <c r="J13" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03130545026922393</v>
+        <v>0.03230091358462006</v>
       </c>
       <c r="M13" t="n">
-        <v>13.15002913277548</v>
+        <v>13.06068625148544</v>
       </c>
       <c r="N13" t="n">
-        <v>299.6656742248254</v>
+        <v>297.2347932099548</v>
       </c>
       <c r="O13" t="n">
-        <v>17.31085423151686</v>
+        <v>17.24049863576906</v>
       </c>
       <c r="P13" t="n">
-        <v>338.042055833699</v>
+        <v>338.0065500544277</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23301,28 +23484,28 @@
         <v>0.0444</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7668174529667703</v>
+        <v>0.7723427226761307</v>
       </c>
       <c r="J14" t="n">
+        <v>356</v>
+      </c>
+      <c r="K14" t="n">
         <v>353</v>
       </c>
-      <c r="K14" t="n">
-        <v>350</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.09550128478450004</v>
+        <v>0.09816901794993538</v>
       </c>
       <c r="M14" t="n">
-        <v>12.73755813834693</v>
+        <v>12.6583560134758</v>
       </c>
       <c r="N14" t="n">
-        <v>309.1989605473606</v>
+        <v>306.7584766205035</v>
       </c>
       <c r="O14" t="n">
-        <v>17.58405415560816</v>
+        <v>17.51452187815881</v>
       </c>
       <c r="P14" t="n">
-        <v>334.0768774754183</v>
+        <v>334.018742918362</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23360,7 +23543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O354"/>
+  <dimension ref="A1:O357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50545,6 +50728,237 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:14+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-38.426098633405125,174.64135296031623</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-38.425403467519374,174.64121319779113</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-38.42470390330363,174.64110687444585</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-38.42399712187571,174.64105545343574</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-38.42329747022113,174.64094969322667</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-38.42260319753917,174.6408029254521</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-38.42190077782126,174.64071099860138</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-38.42121765096304,174.6404705574394</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-38.42053079035821,174.6402668269856</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-38.41983907971889,174.64010129228149</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-38.41914895801713,174.63992518513277</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-38.41845643626431,174.6397649369946</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-38.417774329977604,174.63953563106176</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-38.42609878177297,174.64135183059426</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-38.42540279986874,174.64121828149229</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-38.42470353238852,174.64110969869753</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-38.42399939187142,174.64103816918228</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-38.42330033366505,174.64092789042056</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-38.42260407288623,174.64079626040783</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-38.42190407222962,174.64068661731636</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-38.42122093155272,174.6404479181395</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-38.420524985022574,174.64030529382242</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-38.41983183158744,174.6401493191458</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-38.41914895801713,174.63992518513277</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-38.41845643626431,174.6397649369946</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-38.417774329977604,174.63953563106176</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-38.42609867791549,174.64135262139962</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-38.42540311143906,174.64121590909843</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-38.424704570950695,174.64110179079276</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-38.42400299715352,174.64101071771856</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-38.42330601603147,174.64088462370657</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-38.422606862125214,174.64077502263856</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-38.42190686332167,174.640665960948</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-38.42122808028536,174.64039858473222</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-38.420524985022574,174.64030529382242</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-38.41983183158744,174.6401493191458</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-38.41915915960655,174.63985758820482</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-38.41846643409214,174.63969869036808</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-38.41778585535895,174.6394592625411</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0258/nzd0258.xlsx
+++ b/data/nzd0258/nzd0258.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O357"/>
+  <dimension ref="A1:O359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18606,10 +18606,10 @@
         <v>349.49</v>
       </c>
       <c r="J357" t="n">
-        <v>343.63</v>
+        <v>348.78</v>
       </c>
       <c r="K357" t="n">
-        <v>343.35</v>
+        <v>348.81</v>
       </c>
       <c r="L357" t="n">
         <v>355.14</v>
@@ -18623,6 +18623,108 @@
       <c r="O357" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="C358" t="n">
+        <v>351.21</v>
+      </c>
+      <c r="D358" t="n">
+        <v>349.25</v>
+      </c>
+      <c r="E358" t="n">
+        <v>344.82</v>
+      </c>
+      <c r="F358" t="n">
+        <v>345.14</v>
+      </c>
+      <c r="G358" t="n">
+        <v>342.6</v>
+      </c>
+      <c r="H358" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="I358" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="J358" t="n">
+        <v>350.06</v>
+      </c>
+      <c r="K358" t="n">
+        <v>349.69</v>
+      </c>
+      <c r="L358" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="M358" t="n">
+        <v>354.18</v>
+      </c>
+      <c r="N358" t="n">
+        <v>362.26</v>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>351.2</v>
+      </c>
+      <c r="C359" t="n">
+        <v>354.68</v>
+      </c>
+      <c r="D359" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="E359" t="n">
+        <v>356.97</v>
+      </c>
+      <c r="F359" t="n">
+        <v>350.79</v>
+      </c>
+      <c r="G359" t="n">
+        <v>347.2</v>
+      </c>
+      <c r="H359" t="n">
+        <v>348.9</v>
+      </c>
+      <c r="I359" t="n">
+        <v>358.69</v>
+      </c>
+      <c r="J359" t="n">
+        <v>355.21</v>
+      </c>
+      <c r="K359" t="n">
+        <v>356.29</v>
+      </c>
+      <c r="L359" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="M359" t="n">
+        <v>360.87</v>
+      </c>
+      <c r="N359" t="n">
+        <v>368.97</v>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18637,7 +18739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B374"/>
+  <dimension ref="A1:B376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22380,6 +22482,26 @@
       </c>
       <c r="B374" t="n">
         <v>-0.79</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>
@@ -22548,28 +22670,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.210508628995744</v>
+        <v>1.213428243928675</v>
       </c>
       <c r="J2" t="n">
+        <v>358</v>
+      </c>
+      <c r="K2" t="n">
         <v>356</v>
       </c>
-      <c r="K2" t="n">
-        <v>354</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2999291702824276</v>
+        <v>0.3032066829379947</v>
       </c>
       <c r="M2" t="n">
-        <v>11.19910280944872</v>
+        <v>11.15076245822738</v>
       </c>
       <c r="N2" t="n">
-        <v>190.328657937932</v>
+        <v>189.3026427837574</v>
       </c>
       <c r="O2" t="n">
-        <v>13.79596527749806</v>
+        <v>13.75872969368021</v>
       </c>
       <c r="P2" t="n">
-        <v>316.3876915460861</v>
+        <v>316.3567598077949</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22626,28 +22748,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9720896511852878</v>
+        <v>0.9834456645337599</v>
       </c>
       <c r="J3" t="n">
+        <v>358</v>
+      </c>
+      <c r="K3" t="n">
         <v>356</v>
       </c>
-      <c r="K3" t="n">
-        <v>354</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2692688768643808</v>
+        <v>0.2751106561387147</v>
       </c>
       <c r="M3" t="n">
-        <v>9.868038586171355</v>
+        <v>9.880615522397305</v>
       </c>
       <c r="N3" t="n">
-        <v>142.7017226188771</v>
+        <v>142.5700539050245</v>
       </c>
       <c r="O3" t="n">
-        <v>11.94578262898154</v>
+        <v>11.94027026097083</v>
       </c>
       <c r="P3" t="n">
-        <v>316.4314337756569</v>
+        <v>316.3111056538871</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22704,28 +22826,28 @@
         <v>0.0755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8341433720630894</v>
+        <v>0.8506053135237976</v>
       </c>
       <c r="J4" t="n">
+        <v>358</v>
+      </c>
+      <c r="K4" t="n">
         <v>356</v>
       </c>
-      <c r="K4" t="n">
-        <v>354</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1239353940311274</v>
+        <v>0.1288871431565215</v>
       </c>
       <c r="M4" t="n">
-        <v>13.5479900958601</v>
+        <v>13.55726176902869</v>
       </c>
       <c r="N4" t="n">
-        <v>273.6952873910835</v>
+        <v>273.5799586205767</v>
       </c>
       <c r="O4" t="n">
-        <v>16.54373861589585</v>
+        <v>16.54025267704749</v>
       </c>
       <c r="P4" t="n">
-        <v>314.4673586018528</v>
+        <v>314.292922551474</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22782,28 +22904,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3727297508784115</v>
+        <v>0.3835656869277045</v>
       </c>
       <c r="J5" t="n">
+        <v>358</v>
+      </c>
+      <c r="K5" t="n">
         <v>356</v>
       </c>
-      <c r="K5" t="n">
-        <v>354</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0447570650164314</v>
+        <v>0.04754807375787407</v>
       </c>
       <c r="M5" t="n">
-        <v>10.26056555980174</v>
+        <v>10.26167321856468</v>
       </c>
       <c r="N5" t="n">
-        <v>165.0005846187103</v>
+        <v>164.8742775739194</v>
       </c>
       <c r="O5" t="n">
-        <v>12.84525533489741</v>
+        <v>12.84033790731067</v>
       </c>
       <c r="P5" t="n">
-        <v>330.6987906126772</v>
+        <v>330.5839207669014</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22860,28 +22982,28 @@
         <v>0.0959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6075467829353705</v>
+        <v>0.6106041764530546</v>
       </c>
       <c r="J6" t="n">
+        <v>358</v>
+      </c>
+      <c r="K6" t="n">
         <v>356</v>
       </c>
-      <c r="K6" t="n">
-        <v>354</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1466457239073778</v>
+        <v>0.1491977924300523</v>
       </c>
       <c r="M6" t="n">
-        <v>8.677520785678368</v>
+        <v>8.646607494298951</v>
       </c>
       <c r="N6" t="n">
-        <v>119.8675322208665</v>
+        <v>119.2859407181246</v>
       </c>
       <c r="O6" t="n">
-        <v>10.94840318132587</v>
+        <v>10.92181032238358</v>
       </c>
       <c r="P6" t="n">
-        <v>329.0178511126178</v>
+        <v>328.9855013035721</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22938,28 +23060,28 @@
         <v>0.0877</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5570899146924632</v>
+        <v>0.5541325231238206</v>
       </c>
       <c r="J7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1574593907719544</v>
+        <v>0.1574005708105743</v>
       </c>
       <c r="M7" t="n">
-        <v>7.55120951978305</v>
+        <v>7.523228868693518</v>
       </c>
       <c r="N7" t="n">
-        <v>92.21835858521445</v>
+        <v>91.77661382320058</v>
       </c>
       <c r="O7" t="n">
-        <v>9.603039028620806</v>
+        <v>9.580011159868269</v>
       </c>
       <c r="P7" t="n">
-        <v>333.0490398517105</v>
+        <v>333.0803281252511</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23016,28 +23138,28 @@
         <v>0.0696</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4350873277042783</v>
+        <v>0.4357172253789659</v>
       </c>
       <c r="J8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07416388313148425</v>
+        <v>0.07507865480427156</v>
       </c>
       <c r="M8" t="n">
-        <v>9.160845802649721</v>
+        <v>9.130864888509546</v>
       </c>
       <c r="N8" t="n">
-        <v>131.2317879899634</v>
+        <v>130.5833090473405</v>
       </c>
       <c r="O8" t="n">
-        <v>11.45564437253372</v>
+        <v>11.42730541498478</v>
       </c>
       <c r="P8" t="n">
-        <v>332.9746860763987</v>
+        <v>332.9679710992627</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23094,28 +23216,28 @@
         <v>0.0615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5036192327817853</v>
+        <v>0.5130388107420474</v>
       </c>
       <c r="J9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1083977965757759</v>
+        <v>0.112678377058771</v>
       </c>
       <c r="M9" t="n">
-        <v>8.316871236202093</v>
+        <v>8.320037541050365</v>
       </c>
       <c r="N9" t="n">
-        <v>115.8510068764185</v>
+        <v>115.7259657051568</v>
       </c>
       <c r="O9" t="n">
-        <v>10.76341055968871</v>
+        <v>10.7576003692811</v>
       </c>
       <c r="P9" t="n">
-        <v>332.7128009345144</v>
+        <v>332.6130163476088</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23172,28 +23294,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3263632622673985</v>
+        <v>0.3392884694718755</v>
       </c>
       <c r="J10" t="n">
+        <v>358</v>
+      </c>
+      <c r="K10" t="n">
         <v>356</v>
       </c>
-      <c r="K10" t="n">
-        <v>354</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.04880689017892137</v>
+        <v>0.05280317867481543</v>
       </c>
       <c r="M10" t="n">
-        <v>8.446923103804728</v>
+        <v>8.469215848443675</v>
       </c>
       <c r="N10" t="n">
-        <v>115.8436514509448</v>
+        <v>115.8568920519551</v>
       </c>
       <c r="O10" t="n">
-        <v>10.76306886770427</v>
+        <v>10.76368394426161</v>
       </c>
       <c r="P10" t="n">
-        <v>334.1990124367583</v>
+        <v>334.062423918019</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23250,28 +23372,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2772036120351268</v>
+        <v>0.2925937082410559</v>
       </c>
       <c r="J11" t="n">
+        <v>358</v>
+      </c>
+      <c r="K11" t="n">
         <v>356</v>
       </c>
-      <c r="K11" t="n">
-        <v>354</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.02710425697953522</v>
+        <v>0.03023270298325176</v>
       </c>
       <c r="M11" t="n">
-        <v>9.830892653529322</v>
+        <v>9.855756210967231</v>
       </c>
       <c r="N11" t="n">
-        <v>153.9248413751199</v>
+        <v>154.0721103859225</v>
       </c>
       <c r="O11" t="n">
-        <v>12.40664504913072</v>
+        <v>12.41257871620247</v>
       </c>
       <c r="P11" t="n">
-        <v>333.6451424511677</v>
+        <v>333.4824952158269</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23328,28 +23450,28 @@
         <v>0.1039</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3969485999408561</v>
+        <v>0.4101676118451918</v>
       </c>
       <c r="J12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K12" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04499428765591851</v>
+        <v>0.048149908573758</v>
       </c>
       <c r="M12" t="n">
-        <v>10.85040957651432</v>
+        <v>10.86916315986779</v>
       </c>
       <c r="N12" t="n">
-        <v>185.4997990837507</v>
+        <v>185.4628513462325</v>
       </c>
       <c r="O12" t="n">
-        <v>13.61983109600668</v>
+        <v>13.61847463360829</v>
       </c>
       <c r="P12" t="n">
-        <v>334.8850277458501</v>
+        <v>334.7447529338679</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23406,28 +23528,28 @@
         <v>0.0806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4229352730176432</v>
+        <v>0.4316870375783362</v>
       </c>
       <c r="J13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K13" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03230091358462006</v>
+        <v>0.03391537178194315</v>
       </c>
       <c r="M13" t="n">
-        <v>13.06068625148544</v>
+        <v>13.04411083057427</v>
       </c>
       <c r="N13" t="n">
-        <v>297.2347932099548</v>
+        <v>296.0177280879828</v>
       </c>
       <c r="O13" t="n">
-        <v>17.24049863576906</v>
+        <v>17.20516573846305</v>
       </c>
       <c r="P13" t="n">
-        <v>338.0065500544277</v>
+        <v>337.9136769682016</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23484,28 +23606,28 @@
         <v>0.0444</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7723427226761307</v>
+        <v>0.7840701818590821</v>
       </c>
       <c r="J14" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K14" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09816901794993538</v>
+        <v>0.1016438914915945</v>
       </c>
       <c r="M14" t="n">
-        <v>12.6583560134758</v>
+        <v>12.64832835559405</v>
       </c>
       <c r="N14" t="n">
-        <v>306.7584766205035</v>
+        <v>305.7919916379635</v>
       </c>
       <c r="O14" t="n">
-        <v>17.51452187815881</v>
+        <v>17.48690915050351</v>
       </c>
       <c r="P14" t="n">
-        <v>334.018742918362</v>
+        <v>333.8950024297167</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23543,7 +23665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O357"/>
+  <dimension ref="A1:O359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50930,12 +51052,12 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>-38.420524985022574,174.64030529382242</t>
+          <t>-38.42053372697057,174.6402473686124</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>-38.41983183158744,174.6401493191458</t>
+          <t>-38.419841099686494,174.6400879077437</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -50956,6 +51078,160 @@
       <c r="O357" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-38.42609851471085,174.64135386409376</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-38.42540336366263,174.64121398858907</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-38.42470501604861,174.64109840169067</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-38.42400299715352,174.64101071771856</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-38.4233080189506,174.64086937303537</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-38.42260879085206,174.64076033694602</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-38.42191058477213,174.6406384191209</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-38.42123108339978,174.6403778601927</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-38.42053589972218,174.6402329716647</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-38.419842593443065,174.64007800993375</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-38.41915605330305,174.63987817096543</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-38.41846483851597,174.6397092628361</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-38.41778585535895,174.6394592625411</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-38.42609878177297,174.64135183059426</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-38.4254085119838,174.64117478760141</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-38.42471384380391,174.6410311844894</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-38.424021023468455,174.64087346035544</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-38.423316401516686,174.64080554614242</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-38.42261561556319,174.64070837218097</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-38.42192234390332,174.64055139144216</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-38.4212430958212,174.64029496201618</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-38.4205446416348,174.640175046436</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-38.419853796591006,174.64000377634505</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-38.41917194124399,174.63977289518652</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-38.4184761942448,174.63963401834536</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-38.41779724489948,174.63938379377126</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
